--- a/backend/data/financials_by_company/1300.HK.xlsx
+++ b/backend/data/financials_by_company/1300.HK.xlsx
@@ -662,198 +662,200 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-31444500</v>
+        <v>2473283.687912</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.097565</v>
       </c>
       <c r="D2" t="n">
-        <v>191583000</v>
+        <v>308858000</v>
       </c>
       <c r="E2" t="n">
-        <v>-125778000</v>
+        <v>25350000</v>
       </c>
       <c r="F2" t="n">
-        <v>-125778000</v>
+        <v>25350000</v>
       </c>
       <c r="G2" t="n">
-        <v>-7914000</v>
+        <v>207467000</v>
       </c>
       <c r="H2" t="n">
-        <v>19984000</v>
+        <v>38945000</v>
       </c>
       <c r="I2" t="n">
-        <v>2215543000</v>
+        <v>2438537000</v>
       </c>
       <c r="J2" t="n">
-        <v>65805000</v>
+        <v>334208000</v>
       </c>
       <c r="K2" t="n">
-        <v>45821000</v>
+        <v>295263000</v>
       </c>
       <c r="L2" t="n">
-        <v>-39742000</v>
+        <v>-55434000</v>
       </c>
       <c r="M2" t="n">
-        <v>49153000</v>
+        <v>65366000</v>
       </c>
       <c r="N2" t="n">
-        <v>9411000</v>
+        <v>9932000</v>
       </c>
       <c r="O2" t="n">
-        <v>86419500</v>
+        <v>184590283.687912</v>
       </c>
       <c r="P2" t="n">
-        <v>-7914000</v>
+        <v>207467000</v>
       </c>
       <c r="Q2" t="n">
-        <v>2358259000</v>
+        <v>2604824000</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>1791284000</v>
+        <v>1791500000</v>
       </c>
       <c r="T2" t="n">
-        <v>1791284000</v>
+        <v>1791500000</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0044</v>
+        <v>0.1158</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0044</v>
+        <v>0.1158</v>
       </c>
       <c r="W2" t="n">
-        <v>-7914000</v>
+        <v>207467000</v>
       </c>
       <c r="X2" t="n">
-        <v>-7914000</v>
+        <v>207467000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-7914000</v>
+        <v>207467000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-7914000</v>
+        <v>207467000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-7914000</v>
+        <v>207467000</v>
       </c>
       <c r="AC2" t="n">
-        <v>4582000</v>
+        <v>22430000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-3332000</v>
+        <v>229897000</v>
       </c>
       <c r="AE2" t="n">
-        <v>10914000</v>
+        <v>2921000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-125778000</v>
+        <v>24212000</v>
       </c>
       <c r="AG2" t="n">
-        <v>125778000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>-24212000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
       <c r="AI2" t="n">
-        <v>-39742000</v>
+        <v>-55434000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>49153000</v>
+        <v>65366000</v>
       </c>
       <c r="AK2" t="n">
-        <v>9411000</v>
+        <v>9932000</v>
       </c>
       <c r="AL2" t="n">
-        <v>150893000</v>
+        <v>257632000</v>
       </c>
       <c r="AM2" t="n">
-        <v>142716000</v>
+        <v>166287000</v>
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>54322000</v>
+        <v>58147000</v>
       </c>
       <c r="AP2" t="n">
-        <v>91353000</v>
+        <v>113683000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>48881000</v>
+        <v>71993000</v>
       </c>
       <c r="AR2" t="n">
-        <v>42472000</v>
+        <v>41690000</v>
       </c>
       <c r="AS2" t="n">
-        <v>293609000</v>
+        <v>423919000</v>
       </c>
       <c r="AT2" t="n">
-        <v>2215543000</v>
+        <v>2438537000</v>
       </c>
       <c r="AU2" t="n">
-        <v>2509152000</v>
+        <v>2862456000</v>
       </c>
       <c r="AV2" t="n">
-        <v>2509152000</v>
+        <v>2862456000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-19110594.713656</v>
+        <v>-49390250</v>
       </c>
       <c r="C3" t="n">
-        <v>0.113161</v>
+        <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>220768000</v>
+        <v>258069000</v>
       </c>
       <c r="E3" t="n">
-        <v>-168880000</v>
+        <v>-197561000</v>
       </c>
       <c r="F3" t="n">
-        <v>-168880000</v>
+        <v>-197561000</v>
       </c>
       <c r="G3" t="n">
-        <v>-22547000</v>
+        <v>-56362000</v>
       </c>
       <c r="H3" t="n">
-        <v>22792000</v>
+        <v>23136000</v>
       </c>
       <c r="I3" t="n">
-        <v>2189242000</v>
+        <v>2278036000</v>
       </c>
       <c r="J3" t="n">
-        <v>51888000</v>
+        <v>60508000</v>
       </c>
       <c r="K3" t="n">
-        <v>29096000</v>
+        <v>37372000</v>
       </c>
       <c r="L3" t="n">
-        <v>-42930000</v>
+        <v>-55875000</v>
       </c>
       <c r="M3" t="n">
-        <v>54520000</v>
+        <v>61706000</v>
       </c>
       <c r="N3" t="n">
-        <v>11590000</v>
+        <v>5831000</v>
       </c>
       <c r="O3" t="n">
-        <v>127222405.286344</v>
+        <v>91808750</v>
       </c>
       <c r="P3" t="n">
-        <v>-22547000</v>
+        <v>-56362000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2333943000</v>
+        <v>2408708000</v>
       </c>
       <c r="R3" t="n">
-        <v>1168000</v>
+        <v>1102000</v>
       </c>
       <c r="S3" t="n">
         <v>1791500000</v>
@@ -862,142 +864,140 @@
         <v>1791500000</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0126</v>
+        <v>-0.0315</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0126</v>
+        <v>-0.0315</v>
       </c>
       <c r="W3" t="n">
-        <v>-22547000</v>
+        <v>-56362000</v>
       </c>
       <c r="X3" t="n">
-        <v>-22547000</v>
+        <v>-56362000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-22547000</v>
+        <v>-56362000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-22547000</v>
+        <v>-56362000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-22547000</v>
+        <v>-56362000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2877000</v>
+        <v>32028000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-25424000</v>
+        <v>-24334000</v>
       </c>
       <c r="AE3" t="n">
-        <v>14029000</v>
+        <v>4553000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-168880000</v>
+        <v>-203902000</v>
       </c>
       <c r="AG3" t="n">
-        <v>168880000</v>
+        <v>203902000</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>-42930000</v>
+        <v>-55875000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>54520000</v>
+        <v>61706000</v>
       </c>
       <c r="AK3" t="n">
-        <v>11590000</v>
+        <v>5831000</v>
       </c>
       <c r="AL3" t="n">
-        <v>171820000</v>
+        <v>221618000</v>
       </c>
       <c r="AM3" t="n">
-        <v>144701000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-10812000</v>
-      </c>
+        <v>130672000</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>50023000</v>
+        <v>44195000</v>
       </c>
       <c r="AP3" t="n">
-        <v>97618000</v>
+        <v>88811000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>52689000</v>
+        <v>50146000</v>
       </c>
       <c r="AR3" t="n">
-        <v>44929000</v>
+        <v>38665000</v>
       </c>
       <c r="AS3" t="n">
-        <v>316521000</v>
+        <v>352290000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2189242000</v>
+        <v>2278036000</v>
       </c>
       <c r="AU3" t="n">
-        <v>2505763000</v>
+        <v>2630326000</v>
       </c>
       <c r="AV3" t="n">
-        <v>2505763000</v>
+        <v>2630326000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-49390250</v>
+        <v>-19110594.713656</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25</v>
+        <v>0.113161</v>
       </c>
       <c r="D4" t="n">
-        <v>258069000</v>
+        <v>220768000</v>
       </c>
       <c r="E4" t="n">
-        <v>-197561000</v>
+        <v>-168880000</v>
       </c>
       <c r="F4" t="n">
-        <v>-197561000</v>
+        <v>-168880000</v>
       </c>
       <c r="G4" t="n">
-        <v>-56362000</v>
+        <v>-22547000</v>
       </c>
       <c r="H4" t="n">
-        <v>23136000</v>
+        <v>22792000</v>
       </c>
       <c r="I4" t="n">
-        <v>2278036000</v>
+        <v>2189242000</v>
       </c>
       <c r="J4" t="n">
-        <v>60508000</v>
+        <v>51888000</v>
       </c>
       <c r="K4" t="n">
-        <v>37372000</v>
+        <v>29096000</v>
       </c>
       <c r="L4" t="n">
-        <v>-55875000</v>
+        <v>-42930000</v>
       </c>
       <c r="M4" t="n">
-        <v>61706000</v>
+        <v>54520000</v>
       </c>
       <c r="N4" t="n">
-        <v>5831000</v>
+        <v>11590000</v>
       </c>
       <c r="O4" t="n">
-        <v>91808750</v>
+        <v>127222405.286344</v>
       </c>
       <c r="P4" t="n">
-        <v>-56362000</v>
+        <v>-22547000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2408708000</v>
+        <v>2333943000</v>
       </c>
       <c r="R4" t="n">
-        <v>1102000</v>
+        <v>1168000</v>
       </c>
       <c r="S4" t="n">
         <v>1791500000</v>
@@ -1006,226 +1006,226 @@
         <v>1791500000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0315</v>
+        <v>-0.0126</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0315</v>
+        <v>-0.0126</v>
       </c>
       <c r="W4" t="n">
-        <v>-56362000</v>
+        <v>-22547000</v>
       </c>
       <c r="X4" t="n">
-        <v>-56362000</v>
+        <v>-22547000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-56362000</v>
+        <v>-22547000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-56362000</v>
+        <v>-22547000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-56362000</v>
+        <v>-22547000</v>
       </c>
       <c r="AC4" t="n">
-        <v>32028000</v>
+        <v>-2877000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-24334000</v>
+        <v>-25424000</v>
       </c>
       <c r="AE4" t="n">
-        <v>4553000</v>
+        <v>14029000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-203902000</v>
+        <v>-168880000</v>
       </c>
       <c r="AG4" t="n">
-        <v>203902000</v>
+        <v>168880000</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>-55875000</v>
+        <v>-42930000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>61706000</v>
+        <v>54520000</v>
       </c>
       <c r="AK4" t="n">
-        <v>5831000</v>
+        <v>11590000</v>
       </c>
       <c r="AL4" t="n">
-        <v>221618000</v>
+        <v>171820000</v>
       </c>
       <c r="AM4" t="n">
-        <v>130672000</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>144701000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-10812000</v>
+      </c>
       <c r="AO4" t="n">
-        <v>44195000</v>
+        <v>50023000</v>
       </c>
       <c r="AP4" t="n">
-        <v>88811000</v>
+        <v>97618000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>50146000</v>
+        <v>52689000</v>
       </c>
       <c r="AR4" t="n">
-        <v>38665000</v>
+        <v>44929000</v>
       </c>
       <c r="AS4" t="n">
-        <v>352290000</v>
+        <v>316521000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2278036000</v>
+        <v>2189242000</v>
       </c>
       <c r="AU4" t="n">
-        <v>2630326000</v>
+        <v>2505763000</v>
       </c>
       <c r="AV4" t="n">
-        <v>2630326000</v>
+        <v>2505763000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2473283.687912</v>
+        <v>-31444500</v>
       </c>
       <c r="C5" t="n">
-        <v>0.097565</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>308858000</v>
+        <v>191583000</v>
       </c>
       <c r="E5" t="n">
-        <v>25350000</v>
+        <v>-125778000</v>
       </c>
       <c r="F5" t="n">
-        <v>25350000</v>
+        <v>-125778000</v>
       </c>
       <c r="G5" t="n">
-        <v>207467000</v>
+        <v>-7914000</v>
       </c>
       <c r="H5" t="n">
-        <v>38945000</v>
+        <v>19984000</v>
       </c>
       <c r="I5" t="n">
-        <v>2438537000</v>
+        <v>2215543000</v>
       </c>
       <c r="J5" t="n">
-        <v>334208000</v>
+        <v>65805000</v>
       </c>
       <c r="K5" t="n">
-        <v>295263000</v>
+        <v>45821000</v>
       </c>
       <c r="L5" t="n">
-        <v>-55434000</v>
+        <v>-39742000</v>
       </c>
       <c r="M5" t="n">
-        <v>65366000</v>
+        <v>49153000</v>
       </c>
       <c r="N5" t="n">
-        <v>9932000</v>
+        <v>9411000</v>
       </c>
       <c r="O5" t="n">
-        <v>184590283.687912</v>
+        <v>86419500</v>
       </c>
       <c r="P5" t="n">
-        <v>207467000</v>
+        <v>-7914000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2604824000</v>
+        <v>2358259000</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>1791500000</v>
+        <v>1791284000</v>
       </c>
       <c r="T5" t="n">
-        <v>1791500000</v>
+        <v>1791284000</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1158</v>
+        <v>-0.0044</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1158</v>
+        <v>-0.0044</v>
       </c>
       <c r="W5" t="n">
-        <v>207467000</v>
+        <v>-7914000</v>
       </c>
       <c r="X5" t="n">
-        <v>207467000</v>
+        <v>-7914000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>207467000</v>
+        <v>-7914000</v>
       </c>
       <c r="AA5" t="n">
-        <v>207467000</v>
+        <v>-7914000</v>
       </c>
       <c r="AB5" t="n">
-        <v>207467000</v>
+        <v>-7914000</v>
       </c>
       <c r="AC5" t="n">
-        <v>22430000</v>
+        <v>4582000</v>
       </c>
       <c r="AD5" t="n">
-        <v>229897000</v>
+        <v>-3332000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2921000</v>
+        <v>10914000</v>
       </c>
       <c r="AF5" t="n">
-        <v>24212000</v>
+        <v>-125778000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-24212000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
+        <v>125778000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>-55434000</v>
+        <v>-39742000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>65366000</v>
+        <v>49153000</v>
       </c>
       <c r="AK5" t="n">
-        <v>9932000</v>
+        <v>9411000</v>
       </c>
       <c r="AL5" t="n">
-        <v>257632000</v>
+        <v>150893000</v>
       </c>
       <c r="AM5" t="n">
-        <v>166287000</v>
+        <v>142716000</v>
       </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>58147000</v>
+        <v>54322000</v>
       </c>
       <c r="AP5" t="n">
-        <v>113683000</v>
+        <v>91353000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>71993000</v>
+        <v>48881000</v>
       </c>
       <c r="AR5" t="n">
-        <v>41690000</v>
+        <v>42472000</v>
       </c>
       <c r="AS5" t="n">
-        <v>423919000</v>
+        <v>293609000</v>
       </c>
       <c r="AT5" t="n">
-        <v>2438537000</v>
+        <v>2215543000</v>
       </c>
       <c r="AU5" t="n">
-        <v>2862456000</v>
+        <v>2509152000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2862456000</v>
+        <v>2509152000</v>
       </c>
     </row>
   </sheetData>
@@ -1551,52 +1551,50 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1788070000</v>
+        <v>1791500000</v>
       </c>
       <c r="C2" t="n">
         <v>1791500000</v>
       </c>
       <c r="D2" t="n">
-        <v>1014909000</v>
+        <v>805728000</v>
       </c>
       <c r="E2" t="n">
-        <v>1479454000</v>
+        <v>1266603000</v>
       </c>
       <c r="F2" t="n">
-        <v>3512902000</v>
+        <v>3600955000</v>
       </c>
       <c r="G2" t="n">
-        <v>4992229000</v>
+        <v>4865955000</v>
       </c>
       <c r="H2" t="n">
-        <v>3218324000</v>
+        <v>3163993000</v>
       </c>
       <c r="I2" t="n">
-        <v>3512902000</v>
+        <v>3600955000</v>
       </c>
       <c r="J2" t="n">
-        <v>127000</v>
+        <v>1603000</v>
       </c>
       <c r="K2" t="n">
-        <v>3512902000</v>
+        <v>3600955000</v>
       </c>
       <c r="L2" t="n">
-        <v>3573902000</v>
+        <v>3600955000</v>
       </c>
       <c r="M2" t="n">
-        <v>3512902000</v>
+        <v>3600955000</v>
       </c>
       <c r="N2" t="n">
-        <v>3512902000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>927000</v>
-      </c>
+        <v>3600955000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1719055000</v>
+        <v>1805878000</v>
       </c>
       <c r="Q2" t="n">
         <v>1509865000</v>
@@ -1608,132 +1606,136 @@
         <v>14638000</v>
       </c>
       <c r="T2" t="n">
-        <v>1700994000</v>
+        <v>2008686000</v>
       </c>
       <c r="U2" t="n">
-        <v>86833000</v>
+        <v>24776000</v>
       </c>
       <c r="V2" t="n">
-        <v>482000</v>
+        <v>1588000</v>
       </c>
       <c r="W2" t="n">
-        <v>25351000</v>
+        <v>22194000</v>
       </c>
       <c r="X2" t="n">
-        <v>61000000</v>
+        <v>994000</v>
       </c>
       <c r="Y2" t="n">
+        <v>994000</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>1983910000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1265609000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>609000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1265000000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>704708000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>40219000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>43821000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>620668000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>5609641000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>461738000</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="n">
-        <v>61000000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1614161000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1418454000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>127000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1418327000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>183447000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>39919000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>52082000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>91446000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>5213896000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>381411000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>158233000</v>
+        <v>99168000</v>
       </c>
       <c r="AM2" t="n">
-        <v>172000</v>
+        <v>475000</v>
       </c>
       <c r="AN2" t="n">
-        <v>172000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>475000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
       <c r="AP2" t="n">
-        <v>221759000</v>
+        <v>256160000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-320239000</v>
+        <v>-277370000</v>
       </c>
       <c r="AR2" t="n">
-        <v>541998000</v>
+        <v>533530000</v>
       </c>
       <c r="AS2" t="n">
-        <v>22388000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
+        <v>558000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>256160000</v>
+      </c>
       <c r="AU2" t="n">
-        <v>261433000</v>
+        <v>266951000</v>
       </c>
       <c r="AV2" t="n">
-        <v>199295000</v>
+        <v>200779000</v>
       </c>
       <c r="AW2" t="n">
-        <v>58882000</v>
+        <v>65242000</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>4832485000</v>
+        <v>5147903000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>89680000</v>
+        <v>104449000</v>
       </c>
       <c r="BA2" t="n">
-        <v>5207000</v>
+        <v>16148000</v>
       </c>
       <c r="BB2" t="n">
-        <v>166907000</v>
+        <v>242352000</v>
       </c>
       <c r="BC2" t="n">
-        <v>96397000</v>
+        <v>141230000</v>
       </c>
       <c r="BD2" t="n">
-        <v>25392000</v>
+        <v>41069000</v>
       </c>
       <c r="BE2" t="n">
-        <v>45118000</v>
+        <v>60053000</v>
       </c>
       <c r="BF2" t="n">
-        <v>3075000</v>
+        <v>7968000</v>
       </c>
       <c r="BG2" t="n">
-        <v>4103198000</v>
+        <v>4317714000</v>
       </c>
       <c r="BH2" t="n">
-        <v>464418000</v>
+        <v>459272000</v>
       </c>
       <c r="BI2" t="n">
-        <v>464418000</v>
+        <v>459272000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>464418000</v>
+        <v>459272000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1791500000</v>
@@ -1742,43 +1744,41 @@
         <v>1791500000</v>
       </c>
       <c r="D3" t="n">
-        <v>1145003000</v>
+        <v>1148376000</v>
       </c>
       <c r="E3" t="n">
-        <v>1694977000</v>
+        <v>1686174000</v>
       </c>
       <c r="F3" t="n">
-        <v>3521798000</v>
+        <v>3544427000</v>
       </c>
       <c r="G3" t="n">
-        <v>5216159000</v>
+        <v>5229527000</v>
       </c>
       <c r="H3" t="n">
-        <v>3163821000</v>
+        <v>3040549000</v>
       </c>
       <c r="I3" t="n">
-        <v>3521798000</v>
+        <v>3544427000</v>
       </c>
       <c r="J3" t="n">
-        <v>616000</v>
+        <v>1074000</v>
       </c>
       <c r="K3" t="n">
-        <v>3521798000</v>
+        <v>3544427000</v>
       </c>
       <c r="L3" t="n">
-        <v>3521798000</v>
+        <v>3544427000</v>
       </c>
       <c r="M3" t="n">
-        <v>3521798000</v>
+        <v>3544427000</v>
       </c>
       <c r="N3" t="n">
-        <v>3521798000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
+        <v>3544427000</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1726969000</v>
+        <v>1749516000</v>
       </c>
       <c r="Q3" t="n">
         <v>1509865000</v>
@@ -1790,132 +1790,134 @@
         <v>14638000</v>
       </c>
       <c r="T3" t="n">
-        <v>1879696000</v>
+        <v>1845363000</v>
       </c>
       <c r="U3" t="n">
-        <v>22148000</v>
+        <v>24514000</v>
       </c>
       <c r="V3" t="n">
-        <v>794000</v>
+        <v>1191000</v>
       </c>
       <c r="W3" t="n">
-        <v>21293000</v>
+        <v>22756000</v>
       </c>
       <c r="X3" t="n">
-        <v>61000</v>
+        <v>567000</v>
       </c>
       <c r="Y3" t="n">
-        <v>61000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
+        <v>567000</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>1857548000</v>
+        <v>1820849000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1694916000</v>
+        <v>1685607000</v>
       </c>
       <c r="AC3" t="n">
-        <v>555000</v>
+        <v>507000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1694361000</v>
+        <v>1685100000</v>
       </c>
       <c r="AE3" t="n">
-        <v>149513000</v>
+        <v>121032000</v>
       </c>
       <c r="AF3" t="n">
-        <v>38524000</v>
+        <v>39152000</v>
       </c>
       <c r="AG3" t="n">
-        <v>49080000</v>
+        <v>53287000</v>
       </c>
       <c r="AH3" t="n">
-        <v>61909000</v>
+        <v>28593000</v>
       </c>
       <c r="AI3" t="n">
-        <v>5401494000</v>
+        <v>5389790000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>380125000</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>528392000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>21840000</v>
+      </c>
       <c r="AL3" t="n">
-        <v>139188000</v>
+        <v>113678000</v>
       </c>
       <c r="AM3" t="n">
-        <v>227000</v>
+        <v>309000</v>
       </c>
       <c r="AN3" t="n">
-        <v>227000</v>
+        <v>309000</v>
       </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>238177000</v>
+        <v>259758000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-316634000</v>
+        <v>-296694000</v>
       </c>
       <c r="AR3" t="n">
-        <v>554811000</v>
+        <v>556452000</v>
       </c>
       <c r="AS3" t="n">
-        <v>22855000</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
+        <v>24964000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>237918000</v>
+      </c>
       <c r="AU3" t="n">
-        <v>271187000</v>
+        <v>268140000</v>
       </c>
       <c r="AV3" t="n">
-        <v>199767000</v>
+        <v>200226000</v>
       </c>
       <c r="AW3" t="n">
-        <v>61002000</v>
+        <v>63122000</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>5021369000</v>
+        <v>4861398000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>178212000</v>
+        <v>36929000</v>
       </c>
       <c r="BA3" t="n">
-        <v>9189000</v>
+        <v>13799000</v>
       </c>
       <c r="BB3" t="n">
-        <v>175334000</v>
+        <v>172607000</v>
       </c>
       <c r="BC3" t="n">
-        <v>106834000</v>
+        <v>95422000</v>
       </c>
       <c r="BD3" t="n">
-        <v>22086000</v>
+        <v>22522000</v>
       </c>
       <c r="BE3" t="n">
-        <v>46414000</v>
+        <v>54663000</v>
       </c>
       <c r="BF3" t="n">
-        <v>11469000</v>
+        <v>8393000</v>
       </c>
       <c r="BG3" t="n">
-        <v>4097807000</v>
+        <v>4092946000</v>
       </c>
       <c r="BH3" t="n">
-        <v>549358000</v>
+        <v>536724000</v>
       </c>
       <c r="BI3" t="n">
-        <v>549358000</v>
+        <v>536724000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>549358000</v>
+        <v>536724000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1791500000</v>
@@ -1924,41 +1926,43 @@
         <v>1791500000</v>
       </c>
       <c r="D4" t="n">
-        <v>1148376000</v>
+        <v>1145003000</v>
       </c>
       <c r="E4" t="n">
-        <v>1686174000</v>
+        <v>1694977000</v>
       </c>
       <c r="F4" t="n">
-        <v>3544427000</v>
+        <v>3521798000</v>
       </c>
       <c r="G4" t="n">
-        <v>5229527000</v>
+        <v>5216159000</v>
       </c>
       <c r="H4" t="n">
-        <v>3040549000</v>
+        <v>3163821000</v>
       </c>
       <c r="I4" t="n">
-        <v>3544427000</v>
+        <v>3521798000</v>
       </c>
       <c r="J4" t="n">
-        <v>1074000</v>
+        <v>616000</v>
       </c>
       <c r="K4" t="n">
-        <v>3544427000</v>
+        <v>3521798000</v>
       </c>
       <c r="L4" t="n">
-        <v>3544427000</v>
+        <v>3521798000</v>
       </c>
       <c r="M4" t="n">
-        <v>3544427000</v>
+        <v>3521798000</v>
       </c>
       <c r="N4" t="n">
-        <v>3544427000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>3521798000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>1749516000</v>
+        <v>1726969000</v>
       </c>
       <c r="Q4" t="n">
         <v>1509865000</v>
@@ -1970,177 +1974,177 @@
         <v>14638000</v>
       </c>
       <c r="T4" t="n">
-        <v>1845363000</v>
+        <v>1879696000</v>
       </c>
       <c r="U4" t="n">
-        <v>24514000</v>
+        <v>22148000</v>
       </c>
       <c r="V4" t="n">
-        <v>1191000</v>
+        <v>794000</v>
       </c>
       <c r="W4" t="n">
-        <v>22756000</v>
+        <v>21293000</v>
       </c>
       <c r="X4" t="n">
-        <v>567000</v>
+        <v>61000</v>
       </c>
       <c r="Y4" t="n">
-        <v>567000</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+        <v>61000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
       <c r="AA4" t="n">
-        <v>1820849000</v>
+        <v>1857548000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1685607000</v>
+        <v>1694916000</v>
       </c>
       <c r="AC4" t="n">
-        <v>507000</v>
+        <v>555000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1685100000</v>
+        <v>1694361000</v>
       </c>
       <c r="AE4" t="n">
-        <v>121032000</v>
+        <v>149513000</v>
       </c>
       <c r="AF4" t="n">
-        <v>39152000</v>
+        <v>38524000</v>
       </c>
       <c r="AG4" t="n">
-        <v>53287000</v>
+        <v>49080000</v>
       </c>
       <c r="AH4" t="n">
-        <v>28593000</v>
+        <v>61909000</v>
       </c>
       <c r="AI4" t="n">
-        <v>5389790000</v>
+        <v>5401494000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>528392000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>21840000</v>
-      </c>
+        <v>380125000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>113678000</v>
+        <v>139188000</v>
       </c>
       <c r="AM4" t="n">
-        <v>309000</v>
+        <v>227000</v>
       </c>
       <c r="AN4" t="n">
-        <v>309000</v>
+        <v>227000</v>
       </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>259758000</v>
+        <v>238177000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-296694000</v>
+        <v>-316634000</v>
       </c>
       <c r="AR4" t="n">
-        <v>556452000</v>
+        <v>554811000</v>
       </c>
       <c r="AS4" t="n">
-        <v>24964000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>237918000</v>
-      </c>
+        <v>22855000</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>268140000</v>
+        <v>271187000</v>
       </c>
       <c r="AV4" t="n">
-        <v>200226000</v>
+        <v>199767000</v>
       </c>
       <c r="AW4" t="n">
-        <v>63122000</v>
+        <v>61002000</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>4861398000</v>
+        <v>5021369000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>36929000</v>
+        <v>178212000</v>
       </c>
       <c r="BA4" t="n">
-        <v>13799000</v>
+        <v>9189000</v>
       </c>
       <c r="BB4" t="n">
-        <v>172607000</v>
+        <v>175334000</v>
       </c>
       <c r="BC4" t="n">
-        <v>95422000</v>
+        <v>106834000</v>
       </c>
       <c r="BD4" t="n">
-        <v>22522000</v>
+        <v>22086000</v>
       </c>
       <c r="BE4" t="n">
-        <v>54663000</v>
+        <v>46414000</v>
       </c>
       <c r="BF4" t="n">
-        <v>8393000</v>
+        <v>11469000</v>
       </c>
       <c r="BG4" t="n">
-        <v>4092946000</v>
+        <v>4097807000</v>
       </c>
       <c r="BH4" t="n">
-        <v>536724000</v>
+        <v>549358000</v>
       </c>
       <c r="BI4" t="n">
-        <v>536724000</v>
+        <v>549358000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>536724000</v>
+        <v>549358000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1791500000</v>
+        <v>1788070000</v>
       </c>
       <c r="C5" t="n">
         <v>1791500000</v>
       </c>
       <c r="D5" t="n">
-        <v>805728000</v>
+        <v>1014909000</v>
       </c>
       <c r="E5" t="n">
-        <v>1266603000</v>
+        <v>1479454000</v>
       </c>
       <c r="F5" t="n">
-        <v>3600955000</v>
+        <v>3512902000</v>
       </c>
       <c r="G5" t="n">
-        <v>4865955000</v>
+        <v>4992229000</v>
       </c>
       <c r="H5" t="n">
-        <v>3163993000</v>
+        <v>3218324000</v>
       </c>
       <c r="I5" t="n">
-        <v>3600955000</v>
+        <v>3512902000</v>
       </c>
       <c r="J5" t="n">
-        <v>1603000</v>
+        <v>127000</v>
       </c>
       <c r="K5" t="n">
-        <v>3600955000</v>
+        <v>3512902000</v>
       </c>
       <c r="L5" t="n">
-        <v>3600955000</v>
+        <v>3573902000</v>
       </c>
       <c r="M5" t="n">
-        <v>3600955000</v>
+        <v>3512902000</v>
       </c>
       <c r="N5" t="n">
-        <v>3600955000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>3512902000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>927000</v>
+      </c>
       <c r="P5" t="n">
-        <v>1805878000</v>
+        <v>1719055000</v>
       </c>
       <c r="Q5" t="n">
         <v>1509865000</v>
@@ -2152,131 +2156,127 @@
         <v>14638000</v>
       </c>
       <c r="T5" t="n">
-        <v>2008686000</v>
+        <v>1700994000</v>
       </c>
       <c r="U5" t="n">
-        <v>24776000</v>
+        <v>86833000</v>
       </c>
       <c r="V5" t="n">
-        <v>1588000</v>
+        <v>482000</v>
       </c>
       <c r="W5" t="n">
-        <v>22194000</v>
+        <v>25351000</v>
       </c>
       <c r="X5" t="n">
-        <v>994000</v>
+        <v>61000000</v>
       </c>
       <c r="Y5" t="n">
-        <v>994000</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>61000000</v>
+      </c>
       <c r="AA5" t="n">
-        <v>1983910000</v>
+        <v>1614161000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1265609000</v>
+        <v>1418454000</v>
       </c>
       <c r="AC5" t="n">
-        <v>609000</v>
+        <v>127000</v>
       </c>
       <c r="AD5" t="n">
-        <v>1265000000</v>
+        <v>1418327000</v>
       </c>
       <c r="AE5" t="n">
-        <v>704708000</v>
+        <v>183447000</v>
       </c>
       <c r="AF5" t="n">
-        <v>40219000</v>
+        <v>39919000</v>
       </c>
       <c r="AG5" t="n">
-        <v>43821000</v>
+        <v>52082000</v>
       </c>
       <c r="AH5" t="n">
-        <v>620668000</v>
+        <v>91446000</v>
       </c>
       <c r="AI5" t="n">
-        <v>5609641000</v>
+        <v>5213896000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>461738000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
+        <v>381411000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>99168000</v>
+        <v>158233000</v>
       </c>
       <c r="AM5" t="n">
-        <v>475000</v>
+        <v>172000</v>
       </c>
       <c r="AN5" t="n">
-        <v>475000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
+        <v>172000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>256160000</v>
+        <v>221759000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-277370000</v>
+        <v>-320239000</v>
       </c>
       <c r="AR5" t="n">
-        <v>533530000</v>
+        <v>541998000</v>
       </c>
       <c r="AS5" t="n">
-        <v>558000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>256160000</v>
-      </c>
+        <v>22388000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>266951000</v>
+        <v>261433000</v>
       </c>
       <c r="AV5" t="n">
-        <v>200779000</v>
+        <v>199295000</v>
       </c>
       <c r="AW5" t="n">
-        <v>65242000</v>
+        <v>58882000</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>5147903000</v>
+        <v>4832485000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>104449000</v>
+        <v>89680000</v>
       </c>
       <c r="BA5" t="n">
-        <v>16148000</v>
+        <v>5207000</v>
       </c>
       <c r="BB5" t="n">
-        <v>242352000</v>
+        <v>166907000</v>
       </c>
       <c r="BC5" t="n">
-        <v>141230000</v>
+        <v>96397000</v>
       </c>
       <c r="BD5" t="n">
-        <v>41069000</v>
+        <v>25392000</v>
       </c>
       <c r="BE5" t="n">
-        <v>60053000</v>
+        <v>45118000</v>
       </c>
       <c r="BF5" t="n">
-        <v>7968000</v>
+        <v>3075000</v>
       </c>
       <c r="BG5" t="n">
-        <v>4317714000</v>
+        <v>4103198000</v>
       </c>
       <c r="BH5" t="n">
-        <v>459272000</v>
+        <v>464418000</v>
       </c>
       <c r="BI5" t="n">
-        <v>459272000</v>
+        <v>464418000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>459272000</v>
+        <v>464418000</v>
       </c>
     </row>
   </sheetData>
@@ -2507,474 +2507,474 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>461537000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-927000</v>
-      </c>
+        <v>43218000</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>-1948031000</v>
+        <v>-1685000000</v>
       </c>
       <c r="E2" t="n">
-        <v>1339000000</v>
+        <v>1525000000</v>
       </c>
       <c r="F2" t="n">
-        <v>-8451000</v>
+        <v>-4551000</v>
       </c>
       <c r="G2" t="n">
-        <v>464418000</v>
+        <v>459272000</v>
       </c>
       <c r="H2" t="n">
-        <v>549358000</v>
+        <v>686988000</v>
       </c>
       <c r="I2" t="n">
-        <v>-84940000</v>
+        <v>-227716000</v>
       </c>
       <c r="J2" t="n">
-        <v>-659861000</v>
+        <v>-216886000</v>
       </c>
       <c r="K2" t="n">
-        <v>-49406000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-927000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-927000</v>
-      </c>
+        <v>-56402000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-609031000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>-609031000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-1948031000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1339000000</v>
-      </c>
+        <v>-160000000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-160000000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-1685000000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1525000000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>104933000</v>
+        <v>-58599000</v>
       </c>
       <c r="V2" t="n">
-        <v>89818000</v>
+        <v>-114057000</v>
       </c>
       <c r="W2" t="n">
-        <v>18701000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+        <v>8871000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>51138000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>51138000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
       <c r="AA2" t="n">
-        <v>-3586000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>4865000</v>
-      </c>
+        <v>-4551000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>-8451000</v>
+        <v>-4551000</v>
       </c>
       <c r="AD2" t="n">
-        <v>469988000</v>
+        <v>47769000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-19403000</v>
+        <v>-40900000</v>
       </c>
       <c r="AF2" t="n">
-        <v>307617000</v>
+        <v>-214055000</v>
       </c>
       <c r="AG2" t="n">
-        <v>427273000</v>
+        <v>189964000</v>
       </c>
       <c r="AH2" t="n">
-        <v>8276000</v>
+        <v>-85560000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-127932000</v>
+        <v>-318459000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>39430000</v>
+        <v>55037000</v>
       </c>
       <c r="AK2" t="n">
-        <v>19984000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>38945000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>14543000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>19984000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>24402000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-1138000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-85000</v>
-      </c>
+        <v>572000</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>-3332000</v>
+        <v>229897000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>666566000</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
+        <v>163021000</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>-1943819000</v>
+        <v>-1471000000</v>
       </c>
       <c r="E3" t="n">
-        <v>1327000000</v>
+        <v>1416000000</v>
       </c>
       <c r="F3" t="n">
-        <v>-1756000</v>
+        <v>-27656000</v>
       </c>
       <c r="G3" t="n">
-        <v>549358000</v>
+        <v>536724000</v>
       </c>
       <c r="H3" t="n">
-        <v>536724000</v>
+        <v>459272000</v>
       </c>
       <c r="I3" t="n">
-        <v>12634000</v>
+        <v>77452000</v>
       </c>
       <c r="J3" t="n">
-        <v>-672414000</v>
+        <v>-117027000</v>
       </c>
       <c r="K3" t="n">
-        <v>-55117000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
+        <v>-61293000</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>-616819000</v>
+        <v>-55000000</v>
       </c>
       <c r="O3" t="n">
-        <v>-616819000</v>
+        <v>-55000000</v>
       </c>
       <c r="P3" t="n">
-        <v>-1943819000</v>
+        <v>-1471000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1327000000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-616819000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-1943819000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1327000000</v>
-      </c>
+        <v>1416000000</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>16726000</v>
+        <v>3802000</v>
       </c>
       <c r="V3" t="n">
-        <v>10831000</v>
+        <v>18808000</v>
       </c>
       <c r="W3" t="n">
-        <v>7407000</v>
+        <v>6309000</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>6341000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>6341000</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>-1512000</v>
+        <v>-27656000</v>
       </c>
       <c r="AB3" t="n">
-        <v>244000</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1756000</v>
+        <v>-27656000</v>
       </c>
       <c r="AD3" t="n">
-        <v>668322000</v>
+        <v>190677000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-24855000</v>
+        <v>-38175000</v>
       </c>
       <c r="AF3" t="n">
-        <v>484386000</v>
+        <v>-22293000</v>
       </c>
       <c r="AG3" t="n">
-        <v>655137000</v>
+        <v>-116187000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-6055000</v>
+        <v>68514000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-164696000</v>
+        <v>25380000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>42533000</v>
+        <v>55478000</v>
       </c>
       <c r="AK3" t="n">
-        <v>22792000</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>23136000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
       <c r="AM3" t="n">
-        <v>22792000</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>23136000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-6341000</v>
+      </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>-2931000</v>
       </c>
       <c r="AP3" t="n">
-        <v>10000</v>
+        <v>1004000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-25424000</v>
+        <v>-24334000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>163021000</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>666566000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
       <c r="D4" t="n">
-        <v>-1471000000</v>
+        <v>-1943819000</v>
       </c>
       <c r="E4" t="n">
-        <v>1416000000</v>
+        <v>1327000000</v>
       </c>
       <c r="F4" t="n">
-        <v>-27656000</v>
+        <v>-1756000</v>
       </c>
       <c r="G4" t="n">
+        <v>549358000</v>
+      </c>
+      <c r="H4" t="n">
         <v>536724000</v>
       </c>
-      <c r="H4" t="n">
-        <v>459272000</v>
-      </c>
       <c r="I4" t="n">
-        <v>77452000</v>
+        <v>12634000</v>
       </c>
       <c r="J4" t="n">
-        <v>-117027000</v>
+        <v>-672414000</v>
       </c>
       <c r="K4" t="n">
-        <v>-61293000</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+        <v>-55117000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
       <c r="N4" t="n">
-        <v>-55000000</v>
+        <v>-616819000</v>
       </c>
       <c r="O4" t="n">
-        <v>-55000000</v>
+        <v>-616819000</v>
       </c>
       <c r="P4" t="n">
-        <v>-1471000000</v>
+        <v>-1943819000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1416000000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+        <v>1327000000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-616819000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-1943819000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1327000000</v>
+      </c>
       <c r="U4" t="n">
-        <v>3802000</v>
+        <v>16726000</v>
       </c>
       <c r="V4" t="n">
-        <v>18808000</v>
+        <v>10831000</v>
       </c>
       <c r="W4" t="n">
-        <v>6309000</v>
+        <v>7407000</v>
       </c>
       <c r="X4" t="n">
-        <v>6341000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>6341000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>-27656000</v>
+        <v>-1512000</v>
       </c>
       <c r="AB4" t="n">
+        <v>244000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-1756000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>668322000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-24855000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>484386000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>655137000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-6055000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-164696000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>42533000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>22792000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>22792000</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
         <v>0</v>
       </c>
-      <c r="AC4" t="n">
-        <v>-27656000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>190677000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-38175000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-22293000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-116187000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>68514000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>25380000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>55478000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>23136000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>23136000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-6341000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-2931000</v>
-      </c>
       <c r="AP4" t="n">
-        <v>1004000</v>
+        <v>10000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-24334000</v>
+        <v>-25424000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>43218000</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>461537000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-927000</v>
+      </c>
       <c r="D5" t="n">
-        <v>-1685000000</v>
+        <v>-1948031000</v>
       </c>
       <c r="E5" t="n">
-        <v>1525000000</v>
+        <v>1339000000</v>
       </c>
       <c r="F5" t="n">
-        <v>-4551000</v>
+        <v>-8451000</v>
       </c>
       <c r="G5" t="n">
-        <v>459272000</v>
+        <v>464418000</v>
       </c>
       <c r="H5" t="n">
-        <v>686988000</v>
+        <v>549358000</v>
       </c>
       <c r="I5" t="n">
-        <v>-227716000</v>
+        <v>-84940000</v>
       </c>
       <c r="J5" t="n">
-        <v>-216886000</v>
+        <v>-659861000</v>
       </c>
       <c r="K5" t="n">
-        <v>-56402000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>-49406000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-927000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-927000</v>
+      </c>
       <c r="N5" t="n">
-        <v>-160000000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-160000000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-1685000000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1525000000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+        <v>-609031000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>-609031000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-1948031000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1339000000</v>
+      </c>
       <c r="U5" t="n">
-        <v>-58599000</v>
+        <v>104933000</v>
       </c>
       <c r="V5" t="n">
-        <v>-114057000</v>
+        <v>89818000</v>
       </c>
       <c r="W5" t="n">
-        <v>8871000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>51138000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>51138000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
+        <v>18701000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>-4551000</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>-3586000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4865000</v>
+      </c>
       <c r="AC5" t="n">
-        <v>-4551000</v>
+        <v>-8451000</v>
       </c>
       <c r="AD5" t="n">
-        <v>47769000</v>
+        <v>469988000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-40900000</v>
+        <v>-19403000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-214055000</v>
+        <v>307617000</v>
       </c>
       <c r="AG5" t="n">
-        <v>189964000</v>
+        <v>427273000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-85560000</v>
+        <v>8276000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-318459000</v>
+        <v>-127932000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>55037000</v>
+        <v>39430000</v>
       </c>
       <c r="AK5" t="n">
-        <v>38945000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>14543000</v>
-      </c>
+        <v>19984000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>24402000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-1138000</v>
-      </c>
+        <v>19984000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>572000</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>-1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-85000</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>229897000</v>
+        <v>-3332000</v>
       </c>
     </row>
   </sheetData>
@@ -3514,187 +3514,187 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Lirong  Qian', 'age': 60, 'title': 'Group CEO &amp; Executive Chairman', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 1240691, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chenhui  Qian', 'age': 39, 'title': 'Group Vice GM &amp; Executive Director', 'yearBorn': 1986, 'fiscalYear': 2025, 'totalPay': 920961, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yiu Wai  Lee', 'age': 41, 'title': 'CFO &amp; Company Secretary', 'yearBorn': 1984, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Lirong  Qian', 'age': 60, 'title': 'Group CEO &amp; Executive Chairman', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 1239702, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chenhui  Qian', 'age': 39, 'title': 'Group Vice GM &amp; Executive Director', 'yearBorn': 1986, 'fiscalYear': 2025, 'totalPay': 920227, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yiu Wai  Lee', 'age': 41, 'title': 'CFO &amp; Company Secretary', 'yearBorn': 1984, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -3802,28 +3802,28 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="W2" t="n">
-        <v>3.76</v>
+        <v>4.18</v>
       </c>
       <c r="X2" t="n">
-        <v>3.69</v>
+        <v>4.17</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.22</v>
+        <v>4.68</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.76</v>
+        <v>4.18</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.69</v>
+        <v>4.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.22</v>
+        <v>4.68</v>
       </c>
       <c r="AD2" t="n">
         <v>1561593600</v>
@@ -3835,28 +3835,28 @@
         <v>4.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.875</v>
+        <v>2.157</v>
       </c>
       <c r="AH2" t="n">
-        <v>13228000</v>
+        <v>11808000</v>
       </c>
       <c r="AI2" t="n">
-        <v>13228000</v>
+        <v>11808000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>7419166</v>
+        <v>11173197</v>
       </c>
       <c r="AK2" t="n">
-        <v>19967800</v>
+        <v>18169063</v>
       </c>
       <c r="AL2" t="n">
-        <v>19967800</v>
+        <v>18169063</v>
       </c>
       <c r="AM2" t="n">
-        <v>4.01</v>
+        <v>4.35</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.05</v>
+        <v>4.39</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -3865,31 +3865,31 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7248799744</v>
+        <v>7690799616</v>
       </c>
       <c r="AR2" t="n">
-        <v>6647680000</v>
+        <v>7248800000</v>
       </c>
       <c r="AS2" t="n">
         <v>0.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.3</v>
+        <v>4.93</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.3</v>
+        <v>4.93</v>
       </c>
       <c r="AV2" t="n">
         <v>0.265</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.7472947</v>
+        <v>2.9148126</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.5256</v>
+        <v>2.425</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.733275</v>
+        <v>0.98975</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -3906,31 +3906,31 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>8292446208</v>
+        <v>8734445568</v>
       </c>
       <c r="BE2" t="n">
         <v>0.03986</v>
       </c>
       <c r="BF2" t="n">
-        <v>611604240</v>
+        <v>612276080</v>
       </c>
       <c r="BG2" t="n">
         <v>1768000000</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.60317004</v>
+        <v>0.60278</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0047</v>
+        <v>0.00464</v>
       </c>
       <c r="BJ2" t="n">
         <v>1768000000</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.3660836</v>
+        <v>2.364828</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.7328212</v>
+        <v>1.8394572</v>
       </c>
       <c r="BM2" t="n">
         <v>1767139200</v>
@@ -3948,16 +3948,16 @@
         <v>-0.02</v>
       </c>
       <c r="BR2" t="n">
-        <v>3.143</v>
+        <v>3.31</v>
       </c>
       <c r="BS2" t="n">
-        <v>44.673</v>
+        <v>47.054</v>
       </c>
       <c r="BT2" t="n">
-        <v>11.129032</v>
+        <v>11.424242</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>0.023</v>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="BY2" t="n">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
@@ -4072,138 +4072,138 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>1782115693</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>finmb_172336186</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1332120600000</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>4.17 - 4.68</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>11173197</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>4.0499997</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>13.499998</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>0.3 - 4.93</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.5799999</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.117647044</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1142.4242</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1743071269</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1743071269</v>
+      </c>
+      <c r="DX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>6.097561</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1.925</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.7938144</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>3.36025</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>3.395049</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
           <t>TRIGIANT</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>Trigiant Group Limited</t>
         </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DD2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>finmb_172336186</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DJ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>9.042551</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1332120600000</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.3399999</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>3.69 - 4.22</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>7419166</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>12.666666</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>0.3 - 4.3</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.20000029</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.04651169</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1112.9032</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1743071269</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1743071269</v>
-      </c>
-      <c r="EC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>2.5744</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1.6874672</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>3.366725</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>4.591354</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EK2" t="b">
-        <v>0</v>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
